--- a/tests/perf_v2/perf_history/v2.4.2/detection/DETECTION-raw-Vitens-Aeromonas.xlsx
+++ b/tests/perf_v2/perf_history/v2.4.2/detection/DETECTION-raw-Vitens-Aeromonas.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_s" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_tiny" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_x" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2862,6 +2863,817 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>training:epoch</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>training:e2e_time</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>training:gpu_mem</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>training:train/iter_time</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>training:val/f1-score</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/f1-score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/f1-score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/f1-score</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/iter_time</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/iter_time</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/iter_time</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:e2e_time</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/latency</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/latency</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/latency</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>data_group</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>otx_version</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>otx_ref</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>test_branch</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>test_commit</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>cpu_info</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>accelerator_info</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>user_name</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>machine_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C2" t="n">
+        <v>887.655547618866</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8.020000457763672</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3644806562468063</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9239808917045592</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9461902976036072</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.9465517401695251</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.9429918527603148</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.1363690793514251</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8.721365928649902</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5.058299064636231</v>
+      </c>
+      <c r="M2" t="n">
+        <v>138.4453709125519</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.1586161424528877</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.4312413368584974</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.3813750383988866</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>8.406655550003052</v>
+      </c>
+      <c r="R2" t="n">
+        <v>22.85579085350037</v>
+      </c>
+      <c r="S2" t="n">
+        <v>20.21287703514099</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>20250711-154706</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>DETECTION</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>yolox_x</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Vitens-Aeromonas</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2.4.2</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>b7a58e7dd</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>eugene/benchmark/2.4.2</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>b7a58e7dd</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>workstation06</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>33</v>
+      </c>
+      <c r="C3" t="n">
+        <v>685.1343579292297</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7.519999980926514</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3699088530106978</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9307218194007874</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9482684731483459</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9474583268165588</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.943235158920288</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.1367373615503311</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8.707361221313477</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.985018253326416</v>
+      </c>
+      <c r="M3" t="n">
+        <v>140.467175245285</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.1570390080505947</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.4344405813037224</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3818063735961914</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>8.323067426681519</v>
+      </c>
+      <c r="R3" t="n">
+        <v>23.02535080909729</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20.23573780059814</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>20250711-160610</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>DETECTION</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>yolox_x</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Vitens-Aeromonas</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2.4.2</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>b7a58e7dd</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>eugene/benchmark/2.4.2</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>b7a58e7dd</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>workstation06</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>39</v>
+      </c>
+      <c r="C4" t="n">
+        <v>782.214435338974</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8.039999961853027</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3580736640172127</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9348217248916626</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.945036232471466</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.944633722305298</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9383765459060668</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1375169903039932</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.11591911315918</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4.952135562896729</v>
+      </c>
+      <c r="M4" t="n">
+        <v>139.4628834724426</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1622455389994495</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.4440918778473476</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.3690747809859941</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>8.599013566970825</v>
+      </c>
+      <c r="R4" t="n">
+        <v>23.53686952590942</v>
+      </c>
+      <c r="S4" t="n">
+        <v>19.56096339225769</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>20250711-162154</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>DETECTION</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>yolox_x</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Vitens-Aeromonas</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2.4.2</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>b7a58e7dd</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>eugene/benchmark/2.4.2</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>b7a58e7dd</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>workstation06</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>39</v>
+      </c>
+      <c r="C5" t="n">
+        <v>798.9190764427185</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.730000019073486</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3667514010881766</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9340619444847108</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9542708992958068</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.952175796031952</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9481354355812072</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.1465679258108139</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8.902509689331055</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4.881972312927246</v>
+      </c>
+      <c r="M5" t="n">
+        <v>138.1263132095337</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1582658740709412</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.4336165302204636</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.3740845851178439</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8.388091325759888</v>
+      </c>
+      <c r="R5" t="n">
+        <v>22.98167610168457</v>
+      </c>
+      <c r="S5" t="n">
+        <v>19.82648301124573</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>20250711-163914</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>DETECTION</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>yolox_x</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Vitens-Aeromonas</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2.4.2</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>b7a58e7dd</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>eugene/benchmark/2.4.2</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>b7a58e7dd</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>workstation06</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>33</v>
+      </c>
+      <c r="C6" t="n">
+        <v>693.2541952133179</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.71999979019165</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3686776955922444</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9314969182014464</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9499357938766479</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9511986374855042</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.947729229927063</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.1483560353517532</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.873647689819336</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5.057489395141602</v>
+      </c>
+      <c r="M6" t="n">
+        <v>143.1127457618713</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1609308494711822</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.4453601567250377</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.3805856299850176</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>8.529335021972656</v>
+      </c>
+      <c r="R6" t="n">
+        <v>23.604088306427</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20.17103838920593</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>20250711-165648</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>DETECTION</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>yolox_x</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Vitens-Aeromonas</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2.4.2</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>b7a58e7dd</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>eugene/benchmark/2.4.2</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>b7a58e7dd</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>workstation06</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
